--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128723446</v>
       </c>
       <c r="B3" t="n">
-        <v>79113</v>
+        <v>79140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128723443</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128723448</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128723446</v>
       </c>
       <c r="B3" t="n">
-        <v>79140</v>
+        <v>79144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128723448</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128723446</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128723443</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128723448</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128723446</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128723443</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128723448</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128723446</v>
       </c>
       <c r="B3" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128723448</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128723446</v>
       </c>
       <c r="B3" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128723443</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128723448</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43344-2025 artfynd.xlsx
+++ b/artfynd/A 43344-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723447</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128723446</v>
       </c>
       <c r="B3" t="n">
-        <v>79063</v>
+        <v>79065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128723443</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128723448</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
